--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111570</v>
+        <v>111572</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111572</v>
+        <v>111595</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111595</v>
+        <v>111597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111597</v>
+        <v>111598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111598</v>
+        <v>111599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111599</v>
+        <v>111605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 2132-2025 artfynd.xlsx
+++ b/artfynd/A 2132-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135679469</v>
       </c>
       <c r="B2" t="n">
-        <v>111605</v>
+        <v>111606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
